--- a/spreadsheets/domains/cramps-cyb_CRAMPS-CYB_Workbook.xlsx
+++ b/spreadsheets/domains/cramps-cyb_CRAMPS-CYB_Workbook.xlsx
@@ -2,16 +2,16 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Domain Summary" sheetId="1" r:id="R21ebe49cd3714f34"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Preflight Scope" sheetId="2" r:id="R83cbb15926644d6c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Preflight Sources" sheetId="3" r:id="R542c2265ff984487"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Preflight Rows" sheetId="4" r:id="Rd6d9bc94186e4114"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Gotchas" sheetId="5" r:id="R84c0b1353dfa4220"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Full Gate" sheetId="6" r:id="R47256f5c0f54426b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Full Evidence Binder" sheetId="7" r:id="R71be8467b8474505"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Import Log" sheetId="8" r:id="Re5d871522b2c4fc2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Trust Checkpoints" sheetId="9" r:id="R0c09a56ed3c64851"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reliance Positioning" sheetId="10" r:id="R23f434df061f4761"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Domain Summary" sheetId="1" r:id="Rb4078842d6d646c7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Preflight Scope" sheetId="2" r:id="Rc37129b37bc7402f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Preflight Sources" sheetId="3" r:id="Rbbe1fb6161e04c45"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Preflight Rows" sheetId="4" r:id="R2725a534a1d344c7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Failure Modes" sheetId="5" r:id="Rf9be79b11c604c37"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Full Gate" sheetId="6" r:id="R944afeb3014c470c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Full Evidence Binder" sheetId="7" r:id="R27315b577f534087"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Import Log" sheetId="8" r:id="R9188ce8eceac4e87"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Trust Checkpoints" sheetId="9" r:id="R8ab7a52fb91c4fe4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reliance Positioning" sheetId="10" r:id="R7def9ead3e6a4b31"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -250,7 +250,7 @@
     </x:row>
     <x:row r="7">
       <x:c r="A7" t="str">
-        <x:v>Gotchas</x:v>
+        <x:v>Primary failure modes</x:v>
       </x:c>
       <x:c r="B7" t="str">
         <x:v>sensor coverage gaps; duplicate intel feeds; alert suppression; honeypot selection bias</x:v>
@@ -1089,7 +1089,7 @@
   <x:sheetData>
     <x:row r="1">
       <x:c r="A1" t="str">
-        <x:v>Gotcha</x:v>
+        <x:v>Failure mode</x:v>
       </x:c>
       <x:c r="B1" t="str">
         <x:v>Status</x:v>
@@ -1255,7 +1255,7 @@
       <x:c r="B6" t="str"/>
       <x:c r="C6" t="str"/>
       <x:c r="D6" t="str">
-        <x:v>raw rows, source trace, extraction confidence, review status, quarantine log</x:v>
+        <x:v>raw signal rows, source trace, extraction confidence, review status, quarantine log</x:v>
       </x:c>
       <x:c r="E6" t="str"/>
     </x:row>
